--- a/rates-nodispo/week-19/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-19/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -524,7 +524,7 @@
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:08 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.0007914175167077031</v>
+        <v>0.000856775667571041</v>
       </c>
     </row>
     <row r="7">
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.01521280337671474</v>
+        <v>0.01642153362844495</v>
       </c>
     </row>
     <row r="8">
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1842</v>
+        <v>1765</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.08098839254308829</v>
+        <v>0.0840116140701604</v>
       </c>
     </row>
     <row r="9">
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1486</v>
+        <v>1389</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.06533591276820261</v>
+        <v>0.06611452234756533</v>
       </c>
     </row>
     <row r="10">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>19052</v>
+        <v>17492</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.8376714737952866</v>
+        <v>0.8325955542862583</v>
       </c>
     </row>
   </sheetData>
@@ -677,7 +677,7 @@
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,7 +697,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:08 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>18956</v>
+        <v>17433</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.8334505803728456</v>
+        <v>0.8297872340425532</v>
       </c>
     </row>
     <row r="8">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>533</v>
+        <v>458</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.02343475202251143</v>
+        <v>0.02180018087486315</v>
       </c>
     </row>
     <row r="9">
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1016</v>
+        <v>918</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.04467112205416813</v>
+        <v>0.04369555904612309</v>
       </c>
     </row>
     <row r="10">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2239</v>
+        <v>2200</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.09844354555047485</v>
+        <v>0.1047170260364606</v>
       </c>
     </row>
   </sheetData>
@@ -858,7 +858,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:08 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:08 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:08 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:08 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9707,7 +9707,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:08 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:08 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-19/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-19/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -23,12 +23,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="$#,##0"/>
-    <numFmt numFmtId="166" formatCode="$0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +54,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="008A8377"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -134,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,11 +152,10 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -524,7 +527,7 @@
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -544,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -585,7 +588,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.000856775667571041</v>
+        <v>0.0007914175167077031</v>
       </c>
     </row>
     <row r="7">
@@ -600,10 +603,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.01642153362844495</v>
+        <v>0.01521280337671474</v>
       </c>
     </row>
     <row r="8">
@@ -618,10 +621,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1765</v>
+        <v>1842</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.0840116140701604</v>
+        <v>0.08098839254308829</v>
       </c>
     </row>
     <row r="9">
@@ -636,10 +639,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1389</v>
+        <v>1486</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.06611452234756533</v>
+        <v>0.06533591276820261</v>
       </c>
     </row>
     <row r="10">
@@ -654,10 +657,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17492</v>
+        <v>19052</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.8325955542862583</v>
+        <v>0.8376714737952866</v>
       </c>
     </row>
   </sheetData>
@@ -677,7 +680,7 @@
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -753,10 +756,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>17433</v>
+        <v>18956</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.8297872340425532</v>
+        <v>0.8334505803728456</v>
       </c>
     </row>
     <row r="8">
@@ -771,10 +774,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>458</v>
+        <v>533</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.02180018087486315</v>
+        <v>0.02343475202251143</v>
       </c>
     </row>
     <row r="9">
@@ -789,10 +792,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>918</v>
+        <v>1016</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.04369555904612309</v>
+        <v>0.04467112205416813</v>
       </c>
     </row>
     <row r="10">
@@ -807,10 +810,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2200</v>
+        <v>2239</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.1047170260364606</v>
+        <v>0.09844354555047485</v>
       </c>
     </row>
   </sheetData>
@@ -838,7 +841,7 @@
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -858,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -910,7 +913,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>IPM (USD/M)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -920,7 +923,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>BandaRPM</t>
+          <t>Banda IPM</t>
         </is>
       </c>
     </row>
@@ -960,10 +963,10 @@
       <c r="I6" s="14" t="n">
         <v>0.00360073134298212</v>
       </c>
-      <c r="J6" s="15" t="n">
+      <c r="J6" s="13" t="n">
         <v>292.6886777954681</v>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1010,10 +1013,10 @@
       <c r="I7" s="14" t="n">
         <v>0.04347289501159414</v>
       </c>
-      <c r="J7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="J7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -1060,10 +1063,10 @@
       <c r="I8" s="14" t="n">
         <v>0.01694985261200647</v>
       </c>
-      <c r="J8" s="15" t="n">
+      <c r="J8" s="13" t="n">
         <v>545.9679722809763</v>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1110,10 +1113,10 @@
       <c r="I9" s="14" t="n">
         <v>0.01799414587373629</v>
       </c>
-      <c r="J9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="J9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1160,10 +1163,10 @@
       <c r="I10" s="14" t="n">
         <v>0.09569950087695896</v>
       </c>
-      <c r="J10" s="15" t="n">
+      <c r="J10" s="13" t="n">
         <v>423.9344905056519</v>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -1210,10 +1213,10 @@
       <c r="I11" s="14" t="n">
         <v>0.01605027979260954</v>
       </c>
-      <c r="J11" s="15" t="n">
+      <c r="J11" s="13" t="n">
         <v>629.7595727495001</v>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1260,10 +1263,10 @@
       <c r="I12" s="14" t="n">
         <v>0.01577960541847686</v>
       </c>
-      <c r="J12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="J12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1310,10 +1313,10 @@
       <c r="I13" s="14" t="n">
         <v>0.09619597421718734</v>
       </c>
-      <c r="J13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="J13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -1360,10 +1363,10 @@
       <c r="I14" s="14" t="n">
         <v>0.2610457110586331</v>
       </c>
-      <c r="J14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="J14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1410,10 +1413,10 @@
       <c r="I15" s="14" t="n">
         <v>0.0159045384005825</v>
       </c>
-      <c r="J15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="J15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1460,10 +1463,10 @@
       <c r="I16" s="14" t="n">
         <v>0.02001718469129462</v>
       </c>
-      <c r="J16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="J16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1510,10 +1513,10 @@
       <c r="I17" s="14" t="n">
         <v>0.08808383601986841</v>
       </c>
-      <c r="J17" s="15" t="n">
+      <c r="J17" s="13" t="n">
         <v>34.60936550405901</v>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -1560,10 +1563,10 @@
       <c r="I18" s="14" t="n">
         <v>0.007541637503573506</v>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J18" s="13" t="n">
         <v>546.672449995564</v>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K18" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1610,10 +1613,10 @@
       <c r="I19" s="14" t="n">
         <v>0.02632791176175898</v>
       </c>
-      <c r="J19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="J19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1660,10 +1663,10 @@
       <c r="I20" s="14" t="n">
         <v>0.007845503114564969</v>
       </c>
-      <c r="J20" s="15" t="n">
+      <c r="J20" s="13" t="n">
         <v>230.1959132675848</v>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1710,10 +1713,10 @@
       <c r="I21" s="14" t="n">
         <v>0.01973382347157576</v>
       </c>
-      <c r="J21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="J21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1760,10 +1763,10 @@
       <c r="I22" s="14" t="n">
         <v>0.04310690310734801</v>
       </c>
-      <c r="J22" s="15" t="n">
+      <c r="J22" s="13" t="n">
         <v>378.8914575736367</v>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -1810,10 +1813,10 @@
       <c r="I23" s="14" t="n">
         <v>0.02444675907046953</v>
       </c>
-      <c r="J23" s="15" t="n">
+      <c r="J23" s="13" t="n">
         <v>367.9264713810392</v>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1860,10 +1863,10 @@
       <c r="I24" s="14" t="n">
         <v>0.01341043580787969</v>
       </c>
-      <c r="J24" s="15" t="n">
+      <c r="J24" s="13" t="n">
         <v>635.5601098974439</v>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1910,10 +1913,10 @@
       <c r="I25" s="14" t="n">
         <v>0.02364876584284403</v>
       </c>
-      <c r="J25" s="15" t="n">
+      <c r="J25" s="13" t="n">
         <v>522.8931308168392</v>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1960,10 +1963,10 @@
       <c r="I26" s="14" t="n">
         <v>0.03170494731762188</v>
       </c>
-      <c r="J26" s="15" t="n">
+      <c r="J26" s="13" t="n">
         <v>263.5865361790823</v>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -2010,10 +2013,10 @@
       <c r="I27" s="14" t="n">
         <v>0.02416203029844732</v>
       </c>
-      <c r="J27" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="J27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2060,10 +2063,10 @@
       <c r="I28" s="14" t="n">
         <v>0.04266973850707984</v>
       </c>
-      <c r="J28" s="15" t="n">
+      <c r="J28" s="13" t="n">
         <v>86.62990764438796</v>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -2110,10 +2113,10 @@
       <c r="I29" s="14" t="n">
         <v>0.06928577470046782</v>
       </c>
-      <c r="J29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="J29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -2160,10 +2163,10 @@
       <c r="I30" s="14" t="n">
         <v>0.02974205294278763</v>
       </c>
-      <c r="J30" s="15" t="n">
+      <c r="J30" s="13" t="n">
         <v>362.2185409608678</v>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K30" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2210,10 +2213,10 @@
       <c r="I31" s="14" t="n">
         <v>0.02337723100735617</v>
       </c>
-      <c r="J31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="J31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2260,10 +2263,10 @@
       <c r="I32" s="14" t="n">
         <v>0.1406809171488835</v>
       </c>
-      <c r="J32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="J32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -2310,10 +2313,10 @@
       <c r="I33" s="14" t="n">
         <v>0.03668253120313379</v>
       </c>
-      <c r="J33" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="J33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -2360,10 +2363,10 @@
       <c r="I34" s="14" t="n">
         <v>0.03456035508596002</v>
       </c>
-      <c r="J34" s="15" t="n">
+      <c r="J34" s="13" t="n">
         <v>29.47467527979272</v>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -2410,10 +2413,10 @@
       <c r="I35" s="14" t="n">
         <v>0.0271052259871172</v>
       </c>
-      <c r="J35" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="J35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2460,10 +2463,10 @@
       <c r="I36" s="14" t="n">
         <v>0.00311945347714856</v>
       </c>
-      <c r="J36" s="15" t="n">
+      <c r="J36" s="13" t="n">
         <v>49.70809007506256</v>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2510,10 +2513,10 @@
       <c r="I37" s="14" t="n">
         <v>0.05111705353780257</v>
       </c>
-      <c r="J37" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="J37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -2560,10 +2563,10 @@
       <c r="I38" s="14" t="n">
         <v>0.02538706218273868</v>
       </c>
-      <c r="J38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="J38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2610,10 +2613,10 @@
       <c r="I39" s="14" t="n">
         <v>0.01637579031199678</v>
       </c>
-      <c r="J39" s="15" t="n">
+      <c r="J39" s="13" t="n">
         <v>359.6793382700856</v>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2660,10 +2663,10 @@
       <c r="I40" s="14" t="n">
         <v>0.06581830261223566</v>
       </c>
-      <c r="J40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="J40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -2710,10 +2713,10 @@
       <c r="I41" s="14" t="n">
         <v>0.03095725007557382</v>
       </c>
-      <c r="J41" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="J41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -2760,10 +2763,10 @@
       <c r="I42" s="14" t="n">
         <v>0.01534839344583398</v>
       </c>
-      <c r="J42" s="15" t="n">
+      <c r="J42" s="13" t="n">
         <v>529.6945169754038</v>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="K42" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2810,10 +2813,10 @@
       <c r="I43" s="14" t="n">
         <v>0.03668557705762985</v>
       </c>
-      <c r="J43" s="15" t="n">
+      <c r="J43" s="13" t="n">
         <v>162.0392301749109</v>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="K43" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -2860,10 +2863,10 @@
       <c r="I44" s="14" t="n">
         <v>0.08969289537635604</v>
       </c>
-      <c r="J44" s="15" t="n">
+      <c r="J44" s="13" t="n">
         <v>238.4964818373863</v>
       </c>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="K44" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -2910,10 +2913,10 @@
       <c r="I45" s="14" t="n">
         <v>0.02241565471429185</v>
       </c>
-      <c r="J45" s="15" t="n">
+      <c r="J45" s="13" t="n">
         <v>201.3438941068086</v>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K45" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2960,10 +2963,10 @@
       <c r="I46" s="14" t="n">
         <v>0.01799822567019062</v>
       </c>
-      <c r="J46" s="15" t="n">
+      <c r="J46" s="13" t="n">
         <v>37.48112921906198</v>
       </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3010,10 +3013,10 @@
       <c r="I47" s="14" t="n">
         <v>0.0139631324087655</v>
       </c>
-      <c r="J47" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="J47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3060,10 +3063,10 @@
       <c r="I48" s="14" t="n">
         <v>0.005072243515770964</v>
       </c>
-      <c r="J48" s="15" t="n">
+      <c r="J48" s="13" t="n">
         <v>38.83496812836575</v>
       </c>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="K48" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3110,10 +3113,10 @@
       <c r="I49" s="14" t="n">
         <v>0.04779031157587929</v>
       </c>
-      <c r="J49" s="15" t="n">
+      <c r="J49" s="13" t="n">
         <v>262.2007013602541</v>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="K49" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -3160,10 +3163,10 @@
       <c r="I50" s="14" t="n">
         <v>0.1150648406671294</v>
       </c>
-      <c r="J50" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="J50" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3210,10 +3213,10 @@
       <c r="I51" s="14" t="n">
         <v>0.004232579351702816</v>
       </c>
-      <c r="J51" s="15" t="n">
+      <c r="J51" s="13" t="n">
         <v>295.8020778822188</v>
       </c>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="K51" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3260,10 +3263,10 @@
       <c r="I52" s="14" t="n">
         <v>0.006321993318411913</v>
       </c>
-      <c r="J52" s="15" t="n">
+      <c r="J52" s="13" t="n">
         <v>205.5991902066833</v>
       </c>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="K52" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3310,10 +3313,10 @@
       <c r="I53" s="14" t="n">
         <v>0.0989292007090356</v>
       </c>
-      <c r="J53" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="J53" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3360,10 +3363,10 @@
       <c r="I54" s="14" t="n">
         <v>0.05609865896268294</v>
       </c>
-      <c r="J54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="J54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3410,10 +3413,10 @@
       <c r="I55" s="14" t="n">
         <v>0.02290034539461874</v>
       </c>
-      <c r="J55" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="J55" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3466,7 +3469,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5514,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5566,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>IPM (USD/M)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -5608,7 +5611,7 @@
       <c r="I6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="15" t="n">
+      <c r="J6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -5653,7 +5656,7 @@
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="J7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -5698,7 +5701,7 @@
       <c r="I8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="15" t="n">
+      <c r="J8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -5743,7 +5746,7 @@
       <c r="I9" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="J9" s="13" t="n">
         <v>2121.120195652693</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -5788,7 +5791,7 @@
       <c r="I10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="15" t="n">
+      <c r="J10" s="13" t="n">
         <v>131.9310482003191</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -5833,7 +5836,7 @@
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="15" t="n">
+      <c r="J11" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -5878,7 +5881,7 @@
       <c r="I12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="J12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -5923,7 +5926,7 @@
       <c r="I13" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="J13" s="13" t="n">
         <v>3417.205624960216</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -5968,7 +5971,7 @@
       <c r="I14" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="J14" s="15" t="n">
+      <c r="J14" s="13" t="n">
         <v>1607.286123080711</v>
       </c>
       <c r="K14" s="8" t="inlineStr">
@@ -6013,7 +6016,7 @@
       <c r="I15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="15" t="n">
+      <c r="J15" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -6058,7 +6061,7 @@
       <c r="I16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="15" t="n">
+      <c r="J16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -6103,7 +6106,7 @@
       <c r="I17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="15" t="n">
+      <c r="J17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -6148,7 +6151,7 @@
       <c r="I18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J18" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="8" t="inlineStr">
@@ -6193,7 +6196,7 @@
       <c r="I19" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J19" s="15" t="n">
+      <c r="J19" s="13" t="n">
         <v>589.2838445087184</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -6238,7 +6241,7 @@
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="15" t="n">
+      <c r="J20" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -6283,7 +6286,7 @@
       <c r="I21" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J21" s="15" t="n">
+      <c r="J21" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="7" t="inlineStr">
@@ -6328,7 +6331,7 @@
       <c r="I22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="15" t="n">
+      <c r="J22" s="13" t="n">
         <v>1292.788312493541</v>
       </c>
       <c r="K22" s="8" t="inlineStr">
@@ -6373,7 +6376,7 @@
       <c r="I23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J23" s="15" t="n">
+      <c r="J23" s="13" t="n">
         <v>423.9344905056519</v>
       </c>
       <c r="K23" s="8" t="inlineStr">
@@ -6418,7 +6421,7 @@
       <c r="I24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="15" t="n">
+      <c r="J24" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -6463,7 +6466,7 @@
       <c r="I25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="15" t="n">
+      <c r="J25" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="8" t="inlineStr">
@@ -6508,7 +6511,7 @@
       <c r="I26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="15" t="n">
+      <c r="J26" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -6553,7 +6556,7 @@
       <c r="I27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="15" t="n">
+      <c r="J27" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="8" t="inlineStr">
@@ -6598,7 +6601,7 @@
       <c r="I28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="15" t="n">
+      <c r="J28" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -6643,7 +6646,7 @@
       <c r="I29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="15" t="n">
+      <c r="J29" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="8" t="inlineStr">
@@ -6688,7 +6691,7 @@
       <c r="I30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="15" t="n">
+      <c r="J30" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="7" t="inlineStr">
@@ -6733,7 +6736,7 @@
       <c r="I31" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J31" s="15" t="n">
+      <c r="J31" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="7" t="inlineStr">
@@ -6778,7 +6781,7 @@
       <c r="I32" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="J32" s="15" t="n">
+      <c r="J32" s="13" t="n">
         <v>2611.811753434074</v>
       </c>
       <c r="K32" s="8" t="inlineStr">
@@ -6823,7 +6826,7 @@
       <c r="I33" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="J33" s="15" t="n">
+      <c r="J33" s="13" t="n">
         <v>1960.409728749892</v>
       </c>
       <c r="K33" s="8" t="inlineStr">
@@ -6868,7 +6871,7 @@
       <c r="I34" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J34" s="15" t="n">
+      <c r="J34" s="13" t="n">
         <v>513.9695582213294</v>
       </c>
       <c r="K34" s="7" t="inlineStr">
@@ -6913,7 +6916,7 @@
       <c r="I35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="15" t="n">
+      <c r="J35" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="8" t="inlineStr">
@@ -6958,7 +6961,7 @@
       <c r="I36" s="5" t="n">
         <v>149</v>
       </c>
-      <c r="J36" s="15" t="n">
+      <c r="J36" s="13" t="n">
         <v>13890.6612244096</v>
       </c>
       <c r="K36" s="8" t="inlineStr">
@@ -7003,7 +7006,7 @@
       <c r="I37" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="J37" s="15" t="n">
+      <c r="J37" s="13" t="n">
         <v>17034.85005500076</v>
       </c>
       <c r="K37" s="8" t="inlineStr">
@@ -7048,7 +7051,7 @@
       <c r="I38" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="J38" s="15" t="n">
+      <c r="J38" s="13" t="n">
         <v>818.5025232997056</v>
       </c>
       <c r="K38" s="8" t="inlineStr">
@@ -7093,7 +7096,7 @@
       <c r="I39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="15" t="n">
+      <c r="J39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="7" t="inlineStr">
@@ -7138,7 +7141,7 @@
       <c r="I40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="15" t="n">
+      <c r="J40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="7" t="inlineStr">
@@ -7183,7 +7186,7 @@
       <c r="I41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="15" t="n">
+      <c r="J41" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="8" t="inlineStr">
@@ -7228,7 +7231,7 @@
       <c r="I42" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="J42" s="15" t="n">
+      <c r="J42" s="13" t="n">
         <v>1547.018634709794</v>
       </c>
       <c r="K42" s="8" t="inlineStr">
@@ -7273,7 +7276,7 @@
       <c r="I43" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J43" s="15" t="n">
+      <c r="J43" s="13" t="n">
         <v>2490.812481163542</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
@@ -7318,7 +7321,7 @@
       <c r="I44" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J44" s="15" t="n">
+      <c r="J44" s="13" t="n">
         <v>34.60936550405901</v>
       </c>
       <c r="K44" s="8" t="inlineStr">
@@ -7363,7 +7366,7 @@
       <c r="I45" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J45" s="15" t="n">
+      <c r="J45" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="8" t="inlineStr">
@@ -7408,7 +7411,7 @@
       <c r="I46" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J46" s="15" t="n">
+      <c r="J46" s="13" t="n">
         <v>2159.853129987161</v>
       </c>
       <c r="K46" s="7" t="inlineStr">
@@ -7453,7 +7456,7 @@
       <c r="I47" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="15" t="n">
+      <c r="J47" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="8" t="inlineStr">
@@ -7498,7 +7501,7 @@
       <c r="I48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="15" t="n">
+      <c r="J48" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="7" t="inlineStr">
@@ -7543,7 +7546,7 @@
       <c r="I49" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J49" s="15" t="n">
+      <c r="J49" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K49" s="8" t="inlineStr">
@@ -7588,7 +7591,7 @@
       <c r="I50" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="15" t="n">
+      <c r="J50" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K50" s="7" t="inlineStr">
@@ -7633,7 +7636,7 @@
       <c r="I51" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="J51" s="15" t="n">
+      <c r="J51" s="13" t="n">
         <v>4894.152857872838</v>
       </c>
       <c r="K51" s="8" t="inlineStr">
@@ -7678,7 +7681,7 @@
       <c r="I52" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J52" s="15" t="n">
+      <c r="J52" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K52" s="7" t="inlineStr">
@@ -7723,7 +7726,7 @@
       <c r="I53" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J53" s="15" t="n">
+      <c r="J53" s="13" t="n">
         <v>1558.658260179934</v>
       </c>
       <c r="K53" s="8" t="inlineStr">
@@ -7768,7 +7771,7 @@
       <c r="I54" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J54" s="15" t="n">
+      <c r="J54" s="13" t="n">
         <v>4315.011475936211</v>
       </c>
       <c r="K54" s="8" t="inlineStr">
@@ -7813,7 +7816,7 @@
       <c r="I55" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="15" t="n">
+      <c r="J55" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="8" t="inlineStr">
@@ -7864,7 +7867,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7904,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>IPM (USD/M)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -7911,7 +7914,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>BandaRPM</t>
+          <t>Banda IPM</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7939,7 @@
       <c r="F6" s="14" t="n">
         <v>0.01938432854407861</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="13" t="n">
         <v>227.2283329224914</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -7944,7 +7947,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7971,7 +7974,7 @@
       <c r="F7" s="14" t="n">
         <v>0.0149977314675999</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="13" t="n">
         <v>1183.842179178614</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
@@ -7979,7 +7982,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8006,7 +8009,7 @@
       <c r="F8" s="14" t="n">
         <v>0.04569482237425204</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="13" t="n">
         <v>755.9217846417132</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -8014,7 +8017,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8041,7 +8044,7 @@
       <c r="F9" s="14" t="n">
         <v>0.01215457985807361</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="13" t="n">
         <v>37.53795366464895</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -8049,7 +8052,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8076,7 +8079,7 @@
       <c r="F10" s="14" t="n">
         <v>0.02647629719867082</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="13" t="n">
         <v>1753.92641706044</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -8084,7 +8087,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8111,7 +8114,7 @@
       <c r="F11" s="14" t="n">
         <v>0.03541705110719442</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="13" t="n">
         <v>195.7986521392059</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -8119,7 +8122,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8146,7 +8149,7 @@
       <c r="F12" s="14" t="n">
         <v>0.08386615084971531</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="G12" s="13" t="n">
         <v>82.94797711140292</v>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -8154,7 +8157,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8181,7 +8184,7 @@
       <c r="F13" s="14" t="n">
         <v>0.01341663064013794</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="13" t="n">
         <v>33.34334265872641</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -8189,7 +8192,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8216,7 +8219,7 @@
       <c r="F14" s="14" t="n">
         <v>0.01271295573191117</v>
       </c>
-      <c r="G14" s="15" t="n">
+      <c r="G14" s="13" t="n">
         <v>567.1277743388968</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -8224,7 +8227,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8251,7 +8254,7 @@
       <c r="F15" s="14" t="n">
         <v>0.01886643158975329</v>
       </c>
-      <c r="G15" s="15" t="n">
+      <c r="G15" s="13" t="n">
         <v>362.0073175422006</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -8259,7 +8262,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8286,7 +8289,7 @@
       <c r="F16" s="14" t="n">
         <v>0.1678812515890542</v>
       </c>
-      <c r="G16" s="15" t="n">
+      <c r="G16" s="13" t="n">
         <v>287.1308736104232</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -8294,7 +8297,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8321,7 +8324,7 @@
       <c r="F17" s="14" t="n">
         <v>0.0243457396668747</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="13" t="n">
         <v>3034.21177699089</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
@@ -8329,7 +8332,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8356,7 +8359,7 @@
       <c r="F18" s="14" t="n">
         <v>0.01302072488282326</v>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G18" s="13" t="n">
         <v>832.998744022084</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -8364,7 +8367,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8391,7 +8394,7 @@
       <c r="F19" s="14" t="n">
         <v>0.118925490523766</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G19" s="13" t="n">
         <v>163.5965715990274</v>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -8399,7 +8402,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8426,7 +8429,7 @@
       <c r="F20" s="14" t="n">
         <v>0.02172542767370692</v>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G20" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -8434,7 +8437,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8461,7 +8464,7 @@
       <c r="F21" s="14" t="n">
         <v>0.01881486491753237</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="13" t="n">
         <v>1735.715354354962</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
@@ -8469,7 +8472,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8496,7 +8499,7 @@
       <c r="F22" s="14" t="n">
         <v>0.03699878720866499</v>
       </c>
-      <c r="G22" s="15" t="n">
+      <c r="G22" s="13" t="n">
         <v>3548.207532389019</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -8504,7 +8507,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8531,7 +8534,7 @@
       <c r="F23" s="14" t="n">
         <v>0.02097314004542078</v>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="G23" s="13" t="n">
         <v>2608.155411093064</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -8539,7 +8542,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8566,7 +8569,7 @@
       <c r="F24" s="14" t="n">
         <v>0.04124253698256729</v>
       </c>
-      <c r="G24" s="15" t="n">
+      <c r="G24" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -8574,7 +8577,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8601,7 +8604,7 @@
       <c r="F25" s="14" t="n">
         <v>0.04069506594311697</v>
       </c>
-      <c r="G25" s="15" t="n">
+      <c r="G25" s="13" t="n">
         <v>3942.569225170218</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
@@ -8609,7 +8612,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8636,7 +8639,7 @@
       <c r="F26" s="14" t="n">
         <v>0.03264468843483177</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="G26" s="13" t="n">
         <v>1004.187940233362</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -8644,7 +8647,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8671,7 +8674,7 @@
       <c r="F27" s="14" t="n">
         <v>0.03425159936038495</v>
       </c>
-      <c r="G27" s="15" t="n">
+      <c r="G27" s="13" t="n">
         <v>13283.75657582396</v>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -8679,7 +8682,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8706,7 +8709,7 @@
       <c r="F28" s="14" t="n">
         <v>0.0263774541127312</v>
       </c>
-      <c r="G28" s="15" t="n">
+      <c r="G28" s="13" t="n">
         <v>3961.321590463702</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -8714,7 +8717,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8741,7 +8744,7 @@
       <c r="F29" s="14" t="n">
         <v>0.02599246659616937</v>
       </c>
-      <c r="G29" s="15" t="n">
+      <c r="G29" s="13" t="n">
         <v>1633.470064396811</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
@@ -8749,7 +8752,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8776,7 +8779,7 @@
       <c r="F30" s="14" t="n">
         <v>0.01380145414508033</v>
       </c>
-      <c r="G30" s="15" t="n">
+      <c r="G30" s="13" t="n">
         <v>1763.517396243048</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
@@ -8784,7 +8787,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8811,7 +8814,7 @@
       <c r="F31" s="14" t="n">
         <v>0.01336223830349716</v>
       </c>
-      <c r="G31" s="15" t="n">
+      <c r="G31" s="13" t="n">
         <v>2638.487950631472</v>
       </c>
       <c r="H31" s="10" t="inlineStr">
@@ -8819,7 +8822,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8846,7 +8849,7 @@
       <c r="F32" s="14" t="n">
         <v>0.01701556894224749</v>
       </c>
-      <c r="G32" s="15" t="n">
+      <c r="G32" s="13" t="n">
         <v>634.5417039130086</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -8854,7 +8857,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8881,7 +8884,7 @@
       <c r="F33" s="14" t="n">
         <v>0.01063628230230309</v>
       </c>
-      <c r="G33" s="15" t="n">
+      <c r="G33" s="13" t="n">
         <v>1961.883679784132</v>
       </c>
       <c r="H33" s="10" t="inlineStr">
@@ -8889,7 +8892,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8916,7 +8919,7 @@
       <c r="F34" s="14" t="n">
         <v>0.004575949246490557</v>
       </c>
-      <c r="G34" s="15" t="n">
+      <c r="G34" s="13" t="n">
         <v>937.9612720500276</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -8924,7 +8927,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8951,7 +8954,7 @@
       <c r="F35" s="14" t="n">
         <v>0.007259752861145713</v>
       </c>
-      <c r="G35" s="15" t="n">
+      <c r="G35" s="13" t="n">
         <v>2657.311274615526</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
@@ -8959,7 +8962,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8986,7 +8989,7 @@
       <c r="F36" s="14" t="n">
         <v>0.01940070067722785</v>
       </c>
-      <c r="G36" s="15" t="n">
+      <c r="G36" s="13" t="n">
         <v>2392.455285067274</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -8994,7 +8997,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9021,7 +9024,7 @@
       <c r="F37" s="14" t="n">
         <v>0.01455562378888403</v>
       </c>
-      <c r="G37" s="15" t="n">
+      <c r="G37" s="13" t="n">
         <v>2302.180208523511</v>
       </c>
       <c r="H37" s="10" t="inlineStr">
@@ -9029,7 +9032,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9056,7 +9059,7 @@
       <c r="F38" s="14" t="n">
         <v>0.03166286367288723</v>
       </c>
-      <c r="G38" s="15" t="n">
+      <c r="G38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="9" t="inlineStr">
@@ -9064,7 +9067,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9091,7 +9094,7 @@
       <c r="F39" s="14" t="n">
         <v>0.03270129661040808</v>
       </c>
-      <c r="G39" s="15" t="n">
+      <c r="G39" s="13" t="n">
         <v>51.63061647499331</v>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -9099,7 +9102,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9126,7 +9129,7 @@
       <c r="F40" s="14" t="n">
         <v>0.06100999608797632</v>
       </c>
-      <c r="G40" s="15" t="n">
+      <c r="G40" s="13" t="n">
         <v>2074.957507811455</v>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -9134,7 +9137,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9161,7 +9164,7 @@
       <c r="F41" s="14" t="n">
         <v>0.009386089717686607</v>
       </c>
-      <c r="G41" s="15" t="n">
+      <c r="G41" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="10" t="inlineStr">
@@ -9169,7 +9172,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9196,7 +9199,7 @@
       <c r="F42" s="14" t="n">
         <v>0.03618757805837959</v>
       </c>
-      <c r="G42" s="15" t="n">
+      <c r="G42" s="13" t="n">
         <v>980.7358783044014</v>
       </c>
       <c r="H42" s="9" t="inlineStr">
@@ -9204,7 +9207,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -9231,7 +9234,7 @@
       <c r="F43" s="14" t="n">
         <v>0.01546461729194028</v>
       </c>
-      <c r="G43" s="15" t="n">
+      <c r="G43" s="13" t="n">
         <v>4929.876500006755</v>
       </c>
       <c r="H43" s="10" t="inlineStr">
@@ -9239,7 +9242,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9266,7 +9269,7 @@
       <c r="F44" s="14" t="n">
         <v>0.1001795636157671</v>
       </c>
-      <c r="G44" s="15" t="n">
+      <c r="G44" s="13" t="n">
         <v>22.83842074896283</v>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -9274,7 +9277,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9301,7 +9304,7 @@
       <c r="F45" s="14" t="n">
         <v>0.005654965134882846</v>
       </c>
-      <c r="G45" s="15" t="n">
+      <c r="G45" s="13" t="n">
         <v>595.8381535797814</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
@@ -9309,7 +9312,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9336,7 +9339,7 @@
       <c r="F46" s="14" t="n">
         <v>0.01100832732660367</v>
       </c>
-      <c r="G46" s="15" t="n">
+      <c r="G46" s="13" t="n">
         <v>313.8786063821016</v>
       </c>
       <c r="H46" s="10" t="inlineStr">
@@ -9344,7 +9347,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9371,7 +9374,7 @@
       <c r="F47" s="14" t="n">
         <v>0.03648794940459232</v>
       </c>
-      <c r="G47" s="15" t="n">
+      <c r="G47" s="13" t="n">
         <v>2941.391210920013</v>
       </c>
       <c r="H47" s="9" t="inlineStr">
@@ -9379,7 +9382,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9406,7 +9409,7 @@
       <c r="F48" s="14" t="n">
         <v>0.01149614339256423</v>
       </c>
-      <c r="G48" s="15" t="n">
+      <c r="G48" s="13" t="n">
         <v>332.9765983859108</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
@@ -9414,7 +9417,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9441,7 +9444,7 @@
       <c r="F49" s="14" t="n">
         <v>0.01172032397851101</v>
       </c>
-      <c r="G49" s="15" t="n">
+      <c r="G49" s="13" t="n">
         <v>448.8761473441033</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
@@ -9449,7 +9452,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9476,7 +9479,7 @@
       <c r="F50" s="14" t="n">
         <v>0.03815438754365708</v>
       </c>
-      <c r="G50" s="15" t="n">
+      <c r="G50" s="13" t="n">
         <v>693.0517003516827</v>
       </c>
       <c r="H50" s="9" t="inlineStr">
@@ -9484,7 +9487,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -9511,7 +9514,7 @@
       <c r="F51" s="14" t="n">
         <v>0.02342053757694945</v>
       </c>
-      <c r="G51" s="15" t="n">
+      <c r="G51" s="13" t="n">
         <v>1469.347877893931</v>
       </c>
       <c r="H51" s="10" t="inlineStr">
@@ -9519,7 +9522,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -9546,7 +9549,7 @@
       <c r="F52" s="14" t="n">
         <v>0.01503373354638984</v>
       </c>
-      <c r="G52" s="15" t="n">
+      <c r="G52" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -9554,7 +9557,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9581,7 +9584,7 @@
       <c r="F53" s="14" t="n">
         <v>0.02808519839982701</v>
       </c>
-      <c r="G53" s="15" t="n">
+      <c r="G53" s="13" t="n">
         <v>58.19367859588425</v>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -9589,7 +9592,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9616,7 +9619,7 @@
       <c r="F54" s="14" t="n">
         <v>0.06472314736852849</v>
       </c>
-      <c r="G54" s="15" t="n">
+      <c r="G54" s="13" t="n">
         <v>2749.380228641471</v>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -9624,7 +9627,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9651,7 +9654,7 @@
       <c r="F55" s="14" t="n">
         <v>0.007650064999413319</v>
       </c>
-      <c r="G55" s="15" t="n">
+      <c r="G55" s="13" t="n">
         <v>297.6767889166803</v>
       </c>
       <c r="H55" s="10" t="inlineStr">
@@ -9659,7 +9662,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9707,7 +9710,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9747,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>IPM (USD/M)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -9754,7 +9757,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>BandaRPM</t>
+          <t>Banda IPM</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9782,7 @@
       <c r="F6" s="14" t="n">
         <v>0.02889626797719181</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="13" t="n">
         <v>395.9731809154864</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -9787,7 +9790,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9814,7 +9817,7 @@
       <c r="F7" s="14" t="n">
         <v>0.04055112463555653</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="13" t="n">
         <v>160.1186959879262</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -9822,7 +9825,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9849,7 +9852,7 @@
       <c r="F8" s="14" t="n">
         <v>0.03620916793242569</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="13" t="n">
         <v>208.7322209526501</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -9857,7 +9860,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9884,7 +9887,7 @@
       <c r="F9" s="14" t="n">
         <v>0.03303641047050623</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="13" t="n">
         <v>1551.219377713612</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -9892,7 +9895,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9919,7 +9922,7 @@
       <c r="F10" s="14" t="n">
         <v>0.03792414643410185</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="13" t="n">
         <v>1484.348365642148</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -9927,7 +9930,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -9954,7 +9957,7 @@
       <c r="F11" s="14" t="n">
         <v>0.03956341903814496</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="13" t="n">
         <v>145.5383845666091</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -9962,7 +9965,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9989,7 +9992,7 @@
       <c r="F12" s="14" t="n">
         <v>0.04345626543618901</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="G12" s="13" t="n">
         <v>160.5228093158107</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -9997,7 +10000,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10024,7 +10027,7 @@
       <c r="F13" s="14" t="n">
         <v>0.03048294717649686</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="13" t="n">
         <v>659.2957357786159</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -10032,7 +10035,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10059,7 +10062,7 @@
       <c r="F14" s="14" t="n">
         <v>0.03179385988478052</v>
       </c>
-      <c r="G14" s="15" t="n">
+      <c r="G14" s="13" t="n">
         <v>345.4943176393337</v>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -10067,7 +10070,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10094,7 +10097,7 @@
       <c r="F15" s="14" t="n">
         <v>0.04328426060684157</v>
       </c>
-      <c r="G15" s="15" t="n">
+      <c r="G15" s="13" t="n">
         <v>663.6396472667157</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -10102,7 +10105,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10129,7 +10132,7 @@
       <c r="F16" s="14" t="n">
         <v>0.01849390266388569</v>
       </c>
-      <c r="G16" s="15" t="n">
+      <c r="G16" s="13" t="n">
         <v>344.1420110854566</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -10137,7 +10140,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10164,7 +10167,7 @@
       <c r="F17" s="14" t="n">
         <v>0.03557954395873861</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="13" t="n">
         <v>821.6865746065105</v>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -10172,7 +10175,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10199,7 +10202,7 @@
       <c r="F18" s="14" t="n">
         <v>0.03835858459840904</v>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G18" s="13" t="n">
         <v>597.805823735799</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -10207,7 +10210,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10234,7 +10237,7 @@
       <c r="F19" s="14" t="n">
         <v>0.07392428031532669</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G19" s="13" t="n">
         <v>207.5464861059345</v>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -10242,7 +10245,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10269,7 +10272,7 @@
       <c r="F20" s="14" t="n">
         <v>0.02391355101395904</v>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G20" s="13" t="n">
         <v>1472.92592586803</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -10277,7 +10280,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10304,7 +10307,7 @@
       <c r="F21" s="14" t="n">
         <v>0.0237986659743109</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="13" t="n">
         <v>431.7395559373899</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
@@ -10312,7 +10315,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10339,7 +10342,7 @@
       <c r="F22" s="14" t="n">
         <v>0.01636695236625293</v>
       </c>
-      <c r="G22" s="15" t="n">
+      <c r="G22" s="13" t="n">
         <v>271.3738392436744</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
@@ -10347,7 +10350,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10374,7 +10377,7 @@
       <c r="F23" s="14" t="n">
         <v>0.01404325478120928</v>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="G23" s="13" t="n">
         <v>515.7031696708467</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -10382,7 +10385,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10409,7 +10412,7 @@
       <c r="F24" s="14" t="n">
         <v>0.02289031106929341</v>
       </c>
-      <c r="G24" s="15" t="n">
+      <c r="G24" s="13" t="n">
         <v>595.1909312447058</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -10417,7 +10420,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10444,7 +10447,7 @@
       <c r="F25" s="14" t="n">
         <v>0.06722270907728187</v>
       </c>
-      <c r="G25" s="15" t="n">
+      <c r="G25" s="13" t="n">
         <v>34.63409464536333</v>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -10452,7 +10455,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10479,7 +10482,7 @@
       <c r="F26" s="14" t="n">
         <v>0.04070622629151625</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="G26" s="13" t="n">
         <v>648.579615490899</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -10487,7 +10490,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10514,7 +10517,7 @@
       <c r="F27" s="14" t="n">
         <v>0.01904663222418778</v>
       </c>
-      <c r="G27" s="15" t="n">
+      <c r="G27" s="13" t="n">
         <v>488.0633241829049</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
@@ -10522,7 +10525,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10549,7 +10552,7 @@
       <c r="F28" s="14" t="n">
         <v>0.03750758341472293</v>
       </c>
-      <c r="G28" s="15" t="n">
+      <c r="G28" s="13" t="n">
         <v>48.05560807746134</v>
       </c>
       <c r="H28" s="9" t="inlineStr">
@@ -10557,7 +10560,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10584,7 +10587,7 @@
       <c r="F29" s="14" t="n">
         <v>0.03357846185439427</v>
       </c>
-      <c r="G29" s="15" t="n">
+      <c r="G29" s="13" t="n">
         <v>722.1979784111071</v>
       </c>
       <c r="H29" s="9" t="inlineStr">
@@ -10592,7 +10595,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10619,7 +10622,7 @@
       <c r="F30" s="14" t="n">
         <v>0.03957406027537661</v>
       </c>
-      <c r="G30" s="15" t="n">
+      <c r="G30" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="inlineStr">
@@ -10627,7 +10630,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10654,7 +10657,7 @@
       <c r="F31" s="14" t="n">
         <v>0.01333144986566175</v>
       </c>
-      <c r="G31" s="15" t="n">
+      <c r="G31" s="13" t="n">
         <v>378.3091644954619</v>
       </c>
       <c r="H31" s="10" t="inlineStr">
@@ -10662,7 +10665,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10689,7 +10692,7 @@
       <c r="F32" s="14" t="n">
         <v>0.03063345479143683</v>
       </c>
-      <c r="G32" s="15" t="n">
+      <c r="G32" s="13" t="n">
         <v>247.7343489065674</v>
       </c>
       <c r="H32" s="9" t="inlineStr">
@@ -10697,7 +10700,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10724,7 +10727,7 @@
       <c r="F33" s="14" t="n">
         <v>0.04821970132738546</v>
       </c>
-      <c r="G33" s="15" t="n">
+      <c r="G33" s="13" t="n">
         <v>1692.051344685765</v>
       </c>
       <c r="H33" s="9" t="inlineStr">
@@ -10732,7 +10735,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -10759,7 +10762,7 @@
       <c r="F34" s="14" t="n">
         <v>0.01622106001038958</v>
       </c>
-      <c r="G34" s="15" t="n">
+      <c r="G34" s="13" t="n">
         <v>740.1919404060169</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -10767,7 +10770,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10794,7 +10797,7 @@
       <c r="F35" s="14" t="n">
         <v>0.02571186059097597</v>
       </c>
-      <c r="G35" s="15" t="n">
+      <c r="G35" s="13" t="n">
         <v>920.6815735610954</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
@@ -10802,7 +10805,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10829,7 +10832,7 @@
       <c r="F36" s="14" t="n">
         <v>0.01130035938979457</v>
       </c>
-      <c r="G36" s="15" t="n">
+      <c r="G36" s="13" t="n">
         <v>152.9092581218663</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -10837,7 +10840,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10864,7 +10867,7 @@
       <c r="F37" s="14" t="n">
         <v>0.0291298564731183</v>
       </c>
-      <c r="G37" s="15" t="n">
+      <c r="G37" s="13" t="n">
         <v>321.6318557152768</v>
       </c>
       <c r="H37" s="10" t="inlineStr">
@@ -10872,7 +10875,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10899,7 +10902,7 @@
       <c r="F38" s="14" t="n">
         <v>0.06434093728244902</v>
       </c>
-      <c r="G38" s="15" t="n">
+      <c r="G38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -10907,7 +10910,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10934,7 +10937,7 @@
       <c r="F39" s="14" t="n">
         <v>0.07630819167055203</v>
       </c>
-      <c r="G39" s="15" t="n">
+      <c r="G39" s="13" t="n">
         <v>175.2711436131982</v>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -10942,7 +10945,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10969,7 +10972,7 @@
       <c r="F40" s="14" t="n">
         <v>0.02131987842193988</v>
       </c>
-      <c r="G40" s="15" t="n">
+      <c r="G40" s="13" t="n">
         <v>392.3725835622307</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
@@ -10977,7 +10980,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11004,7 +11007,7 @@
       <c r="F41" s="14" t="n">
         <v>0.03170345511351007</v>
       </c>
-      <c r="G41" s="15" t="n">
+      <c r="G41" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="9" t="inlineStr">
@@ -11012,7 +11015,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11039,7 +11042,7 @@
       <c r="F42" s="14" t="n">
         <v>0.01383787983584153</v>
       </c>
-      <c r="G42" s="15" t="n">
+      <c r="G42" s="13" t="n">
         <v>740.9131147121883</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
@@ -11047,7 +11050,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11074,7 +11077,7 @@
       <c r="F43" s="14" t="n">
         <v>0.049494642935241</v>
       </c>
-      <c r="G43" s="15" t="n">
+      <c r="G43" s="13" t="n">
         <v>6133.692781166868</v>
       </c>
       <c r="H43" s="9" t="inlineStr">
@@ -11082,7 +11085,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -11109,7 +11112,7 @@
       <c r="F44" s="14" t="n">
         <v>0.01358016484352831</v>
       </c>
-      <c r="G44" s="15" t="n">
+      <c r="G44" s="13" t="n">
         <v>355.3514638664063</v>
       </c>
       <c r="H44" s="10" t="inlineStr">
@@ -11117,7 +11120,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11144,7 +11147,7 @@
       <c r="F45" s="14" t="n">
         <v>0.1091779217373222</v>
       </c>
-      <c r="G45" s="15" t="n">
+      <c r="G45" s="13" t="n">
         <v>1545.561175683055</v>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -11152,7 +11155,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -11179,7 +11182,7 @@
       <c r="F46" s="14" t="n">
         <v>0.03053079590592728</v>
       </c>
-      <c r="G46" s="15" t="n">
+      <c r="G46" s="13" t="n">
         <v>102.7545519117548</v>
       </c>
       <c r="H46" s="9" t="inlineStr">
@@ -11187,7 +11190,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11214,7 +11217,7 @@
       <c r="F47" s="14" t="n">
         <v>0.01959781171599037</v>
       </c>
-      <c r="G47" s="15" t="n">
+      <c r="G47" s="13" t="n">
         <v>404.1635959709316</v>
       </c>
       <c r="H47" s="10" t="inlineStr">
@@ -11222,7 +11225,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11249,7 +11252,7 @@
       <c r="F48" s="14" t="n">
         <v>0.03551582289197756</v>
       </c>
-      <c r="G48" s="15" t="n">
+      <c r="G48" s="13" t="n">
         <v>619.8835280695329</v>
       </c>
       <c r="H48" s="9" t="inlineStr">
@@ -11257,7 +11260,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11284,7 +11287,7 @@
       <c r="F49" s="14" t="n">
         <v>0.03598596156000584</v>
       </c>
-      <c r="G49" s="15" t="n">
+      <c r="G49" s="13" t="n">
         <v>888.2808927828733</v>
       </c>
       <c r="H49" s="9" t="inlineStr">
@@ -11292,7 +11295,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11319,7 +11322,7 @@
       <c r="F50" s="14" t="n">
         <v>0.04126390709897875</v>
       </c>
-      <c r="G50" s="15" t="n">
+      <c r="G50" s="13" t="n">
         <v>1481.181036420116</v>
       </c>
       <c r="H50" s="9" t="inlineStr">
@@ -11327,7 +11330,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11354,7 +11357,7 @@
       <c r="F51" s="14" t="n">
         <v>0.03553215608795746</v>
       </c>
-      <c r="G51" s="15" t="n">
+      <c r="G51" s="13" t="n">
         <v>672.9015662522922</v>
       </c>
       <c r="H51" s="9" t="inlineStr">
@@ -11362,7 +11365,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11389,7 +11392,7 @@
       <c r="F52" s="14" t="n">
         <v>0.02412524078768244</v>
       </c>
-      <c r="G52" s="15" t="n">
+      <c r="G52" s="13" t="n">
         <v>804.0700131437338</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -11397,7 +11400,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11424,7 +11427,7 @@
       <c r="F53" s="14" t="n">
         <v>0.005573780456420972</v>
       </c>
-      <c r="G53" s="15" t="n">
+      <c r="G53" s="13" t="n">
         <v>439.2976139233429</v>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -11432,7 +11435,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11459,7 +11462,7 @@
       <c r="F54" s="14" t="n">
         <v>0.08962253368805807</v>
       </c>
-      <c r="G54" s="15" t="n">
+      <c r="G54" s="13" t="n">
         <v>471.2719382828263</v>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -11467,7 +11470,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11494,7 +11497,7 @@
       <c r="F55" s="14" t="n">
         <v>0.05694233971922022</v>
       </c>
-      <c r="G55" s="15" t="n">
+      <c r="G55" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -11502,7 +11505,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11550,7 +11553,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11587,7 +11590,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>IPM (USD/M)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -11597,7 +11600,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>BandaRPM</t>
+          <t>Banda IPM</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11625,7 @@
       <c r="F6" s="14" t="n">
         <v>0.02153161296445639</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="13" t="n">
         <v>475.7083707853917</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -11630,7 +11633,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11657,7 +11660,7 @@
       <c r="F7" s="14" t="n">
         <v>0.03254959789189761</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="13" t="n">
         <v>1330.105704992663</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -11665,7 +11668,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11692,7 +11695,7 @@
       <c r="F8" s="14" t="n">
         <v>0.0413968940727391</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="13" t="n">
         <v>1286.321398345321</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -11700,7 +11703,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11727,7 +11730,7 @@
       <c r="F9" s="14" t="n">
         <v>0.01992570797418616</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="13" t="n">
         <v>755.023993534594</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -11735,7 +11738,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11762,7 +11765,7 @@
       <c r="F10" s="14" t="n">
         <v>0.02670714974795526</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="13" t="n">
         <v>462.8258057565207</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -11770,7 +11773,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11797,7 +11800,7 @@
       <c r="F11" s="14" t="n">
         <v>0.03085502190419258</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="13" t="n">
         <v>944.7434573897368</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -11805,7 +11808,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11832,7 +11835,7 @@
       <c r="F12" s="14" t="n">
         <v>0.01500020317846965</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="G12" s="13" t="n">
         <v>572.9913255101271</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -11840,7 +11843,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11867,7 +11870,7 @@
       <c r="F13" s="14" t="n">
         <v>0.0141750520642641</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="13" t="n">
         <v>592.0593657885341</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -11875,7 +11878,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11902,7 +11905,7 @@
       <c r="F14" s="14" t="n">
         <v>0.06996611405352626</v>
       </c>
-      <c r="G14" s="15" t="n">
+      <c r="G14" s="13" t="n">
         <v>184.7159830151929</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -11910,7 +11913,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11937,7 +11940,7 @@
       <c r="F15" s="14" t="n">
         <v>0.09570783673262082</v>
       </c>
-      <c r="G15" s="15" t="n">
+      <c r="G15" s="13" t="n">
         <v>386.7918474924257</v>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -11945,7 +11948,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11972,7 +11975,7 @@
       <c r="F16" s="14" t="n">
         <v>0.05150828646025968</v>
       </c>
-      <c r="G16" s="15" t="n">
+      <c r="G16" s="13" t="n">
         <v>160.1103987658598</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -11980,7 +11983,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12007,7 +12010,7 @@
       <c r="F17" s="14" t="n">
         <v>0.07634924039435519</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="13" t="n">
         <v>704.2836540644925</v>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -12015,7 +12018,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12042,7 +12045,7 @@
       <c r="F18" s="14" t="n">
         <v>0.05791482341057642</v>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G18" s="13" t="n">
         <v>79.96969333678696</v>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -12050,7 +12053,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12077,7 +12080,7 @@
       <c r="F19" s="14" t="n">
         <v>0.0499106025603893</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G19" s="13" t="n">
         <v>320.2988893866719</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -12085,7 +12088,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -12112,7 +12115,7 @@
       <c r="F20" s="14" t="n">
         <v>0.01937781629369773</v>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G20" s="13" t="n">
         <v>55.52171228380126</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -12120,7 +12123,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12147,7 +12150,7 @@
       <c r="F21" s="14" t="n">
         <v>0.02758930265227551</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="13" t="n">
         <v>459.2477737961996</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
@@ -12155,7 +12158,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -12182,7 +12185,7 @@
       <c r="F22" s="14" t="n">
         <v>0.03550533242881199</v>
       </c>
-      <c r="G22" s="15" t="n">
+      <c r="G22" s="13" t="n">
         <v>547.4982753257368</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -12190,7 +12193,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -12217,7 +12220,7 @@
       <c r="F23" s="14" t="n">
         <v>0.04363089571038412</v>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="G23" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -12225,7 +12228,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12252,7 +12255,7 @@
       <c r="F24" s="14" t="n">
         <v>0.0371935884030042</v>
       </c>
-      <c r="G24" s="15" t="n">
+      <c r="G24" s="13" t="n">
         <v>6.045591141576674</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -12260,7 +12263,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12287,7 +12290,7 @@
       <c r="F25" s="14" t="n">
         <v>0.07321686966100342</v>
       </c>
-      <c r="G25" s="15" t="n">
+      <c r="G25" s="13" t="n">
         <v>2522.09506250974</v>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -12295,7 +12298,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -12322,7 +12325,7 @@
       <c r="F26" s="14" t="n">
         <v>0.04528409293746551</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="G26" s="13" t="n">
         <v>73.29285606812685</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -12330,7 +12333,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12357,7 +12360,7 @@
       <c r="F27" s="14" t="n">
         <v>0.004247591639568573</v>
       </c>
-      <c r="G27" s="15" t="n">
+      <c r="G27" s="13" t="n">
         <v>363.7981464349618</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
@@ -12365,7 +12368,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -12392,7 +12395,7 @@
       <c r="F28" s="14" t="n">
         <v>0.01858171295139898</v>
       </c>
-      <c r="G28" s="15" t="n">
+      <c r="G28" s="13" t="n">
         <v>1758.170133528959</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -12400,7 +12403,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -12427,7 +12430,7 @@
       <c r="F29" s="14" t="n">
         <v>0.1139849172225033</v>
       </c>
-      <c r="G29" s="15" t="n">
+      <c r="G29" s="13" t="n">
         <v>482.4066625309437</v>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -12435,7 +12438,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -12462,7 +12465,7 @@
       <c r="F30" s="14" t="n">
         <v>0.04759110766984132</v>
       </c>
-      <c r="G30" s="15" t="n">
+      <c r="G30" s="13" t="n">
         <v>755.5052057725284</v>
       </c>
       <c r="H30" s="9" t="inlineStr">
@@ -12470,7 +12473,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12497,7 +12500,7 @@
       <c r="F31" s="14" t="n">
         <v>0.03654081168947738</v>
       </c>
-      <c r="G31" s="15" t="n">
+      <c r="G31" s="13" t="n">
         <v>484.1079814290122</v>
       </c>
       <c r="H31" s="9" t="inlineStr">
@@ -12505,7 +12508,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -12532,7 +12535,7 @@
       <c r="F32" s="14" t="n">
         <v>0.02481050666143461</v>
       </c>
-      <c r="G32" s="15" t="n">
+      <c r="G32" s="13" t="n">
         <v>203.5472268448092</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -12540,7 +12543,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -12567,7 +12570,7 @@
       <c r="F33" s="14" t="n">
         <v>0.01522826251942148</v>
       </c>
-      <c r="G33" s="15" t="n">
+      <c r="G33" s="13" t="n">
         <v>784.9293745582175</v>
       </c>
       <c r="H33" s="10" t="inlineStr">
@@ -12575,7 +12578,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12602,7 +12605,7 @@
       <c r="F34" s="14" t="n">
         <v>0.04942994841816553</v>
       </c>
-      <c r="G34" s="15" t="n">
+      <c r="G34" s="13" t="n">
         <v>708.2702198000156</v>
       </c>
       <c r="H34" s="9" t="inlineStr">
@@ -12610,7 +12613,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12637,7 +12640,7 @@
       <c r="F35" s="14" t="n">
         <v>0.01061013773445753</v>
       </c>
-      <c r="G35" s="15" t="n">
+      <c r="G35" s="13" t="n">
         <v>266.8638824303267</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
@@ -12645,7 +12648,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -12672,7 +12675,7 @@
       <c r="F36" s="14" t="n">
         <v>0.01523681436838833</v>
       </c>
-      <c r="G36" s="15" t="n">
+      <c r="G36" s="13" t="n">
         <v>774.9095732847761</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -12680,7 +12683,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12707,7 +12710,7 @@
       <c r="F37" s="14" t="n">
         <v>0.09079600071173426</v>
       </c>
-      <c r="G37" s="15" t="n">
+      <c r="G37" s="13" t="n">
         <v>985.6773766215867</v>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -12715,7 +12718,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12742,7 +12745,7 @@
       <c r="F38" s="14" t="n">
         <v>0.04109951963624363</v>
       </c>
-      <c r="G38" s="15" t="n">
+      <c r="G38" s="13" t="n">
         <v>1393.747020644641</v>
       </c>
       <c r="H38" s="9" t="inlineStr">
@@ -12750,7 +12753,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12777,7 +12780,7 @@
       <c r="F39" s="14" t="n">
         <v>0.02020594086299469</v>
       </c>
-      <c r="G39" s="15" t="n">
+      <c r="G39" s="13" t="n">
         <v>3130.552678975173</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
@@ -12785,7 +12788,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -12812,7 +12815,7 @@
       <c r="F40" s="14" t="n">
         <v>0.04569102090240866</v>
       </c>
-      <c r="G40" s="15" t="n">
+      <c r="G40" s="13" t="n">
         <v>1788.139509867148</v>
       </c>
       <c r="H40" s="9" t="inlineStr">
@@ -12820,7 +12823,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -12847,7 +12850,7 @@
       <c r="F41" s="14" t="n">
         <v>0.005455038686544631</v>
       </c>
-      <c r="G41" s="15" t="n">
+      <c r="G41" s="13" t="n">
         <v>182.8830387284813</v>
       </c>
       <c r="H41" s="10" t="inlineStr">
@@ -12855,7 +12858,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12882,7 +12885,7 @@
       <c r="F42" s="14" t="n">
         <v>0.01904156057940504</v>
       </c>
-      <c r="G42" s="15" t="n">
+      <c r="G42" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
@@ -12890,7 +12893,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12917,7 +12920,7 @@
       <c r="F43" s="14" t="n">
         <v>0.1800727178325176</v>
       </c>
-      <c r="G43" s="15" t="n">
+      <c r="G43" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -12925,7 +12928,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12952,7 +12955,7 @@
       <c r="F44" s="14" t="n">
         <v>0.08721405753644984</v>
       </c>
-      <c r="G44" s="15" t="n">
+      <c r="G44" s="13" t="n">
         <v>752.0705247933588</v>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -12960,7 +12963,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12987,7 +12990,7 @@
       <c r="F45" s="14" t="n">
         <v>0.0217972910319934</v>
       </c>
-      <c r="G45" s="15" t="n">
+      <c r="G45" s="13" t="n">
         <v>1180.265977183201</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
@@ -12995,7 +12998,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -13022,7 +13025,7 @@
       <c r="F46" s="14" t="n">
         <v>0.09019863165026266</v>
       </c>
-      <c r="G46" s="15" t="n">
+      <c r="G46" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -13030,7 +13033,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13057,7 +13060,7 @@
       <c r="F47" s="14" t="n">
         <v>0.02254753052924734</v>
       </c>
-      <c r="G47" s="15" t="n">
+      <c r="G47" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="10" t="inlineStr">
@@ -13065,7 +13068,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13092,7 +13095,7 @@
       <c r="F48" s="14" t="n">
         <v>0.002190383198491984</v>
       </c>
-      <c r="G48" s="15" t="n">
+      <c r="G48" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
@@ -13100,7 +13103,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13127,7 +13130,7 @@
       <c r="F49" s="14" t="n">
         <v>0.02163370542034904</v>
       </c>
-      <c r="G49" s="15" t="n">
+      <c r="G49" s="13" t="n">
         <v>292.9402822694824</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
@@ -13135,7 +13138,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -13162,7 +13165,7 @@
       <c r="F50" s="14" t="n">
         <v>0.0112605904930588</v>
       </c>
-      <c r="G50" s="15" t="n">
+      <c r="G50" s="13" t="n">
         <v>155.6348979359769</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
@@ -13170,7 +13173,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13197,7 +13200,7 @@
       <c r="F51" s="14" t="n">
         <v>0.00701062910165464</v>
       </c>
-      <c r="G51" s="15" t="n">
+      <c r="G51" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="10" t="inlineStr">
@@ -13205,7 +13208,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13232,7 +13235,7 @@
       <c r="F52" s="14" t="n">
         <v>0.03753521912312323</v>
       </c>
-      <c r="G52" s="15" t="n">
+      <c r="G52" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="9" t="inlineStr">
@@ -13240,7 +13243,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13267,7 +13270,7 @@
       <c r="F53" s="14" t="n">
         <v>0.02222823087344108</v>
       </c>
-      <c r="G53" s="15" t="n">
+      <c r="G53" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -13275,7 +13278,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13302,7 +13305,7 @@
       <c r="F54" s="14" t="n">
         <v>0.01645638015893159</v>
       </c>
-      <c r="G54" s="15" t="n">
+      <c r="G54" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -13310,7 +13313,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13337,7 +13340,7 @@
       <c r="F55" s="14" t="n">
         <v>0.03220320300941006</v>
       </c>
-      <c r="G55" s="15" t="n">
+      <c r="G55" s="13" t="n">
         <v>791.9061339905348</v>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -13345,7 +13348,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -13372,7 +13375,7 @@
       <c r="F56" s="14" t="n">
         <v>0.006537468433447777</v>
       </c>
-      <c r="G56" s="15" t="n">
+      <c r="G56" s="13" t="n">
         <v>665.7988820474988</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
@@ -13380,7 +13383,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I56" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -13407,7 +13410,7 @@
       <c r="F57" s="14" t="n">
         <v>0.005539606724511772</v>
       </c>
-      <c r="G57" s="15" t="n">
+      <c r="G57" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="10" t="inlineStr">
@@ -13415,7 +13418,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13442,7 +13445,7 @@
       <c r="F58" s="14" t="n">
         <v>0.02311236871963816</v>
       </c>
-      <c r="G58" s="15" t="n">
+      <c r="G58" s="13" t="n">
         <v>1569.229688455987</v>
       </c>
       <c r="H58" s="10" t="inlineStr">
@@ -13450,7 +13453,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -13477,7 +13480,7 @@
       <c r="F59" s="14" t="n">
         <v>0.01462070171632862</v>
       </c>
-      <c r="G59" s="15" t="n">
+      <c r="G59" s="13" t="n">
         <v>124.0098508333607</v>
       </c>
       <c r="H59" s="10" t="inlineStr">
@@ -13485,7 +13488,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13512,7 +13515,7 @@
       <c r="F60" s="14" t="n">
         <v>0.03203292137414028</v>
       </c>
-      <c r="G60" s="15" t="n">
+      <c r="G60" s="13" t="n">
         <v>620.0604678300537</v>
       </c>
       <c r="H60" s="9" t="inlineStr">
@@ -13520,7 +13523,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -13547,7 +13550,7 @@
       <c r="F61" s="14" t="n">
         <v>0.008132170375370885</v>
       </c>
-      <c r="G61" s="15" t="n">
+      <c r="G61" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="10" t="inlineStr">
@@ -13555,7 +13558,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I61" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13582,7 +13585,7 @@
       <c r="F62" s="14" t="n">
         <v>0.009816834219813371</v>
       </c>
-      <c r="G62" s="15" t="n">
+      <c r="G62" s="13" t="n">
         <v>2556.824332614046</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
@@ -13590,7 +13593,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -13617,7 +13620,7 @@
       <c r="F63" s="14" t="n">
         <v>0.02902103416888524</v>
       </c>
-      <c r="G63" s="15" t="n">
+      <c r="G63" s="13" t="n">
         <v>166.3977774357279</v>
       </c>
       <c r="H63" s="10" t="inlineStr">
@@ -13625,7 +13628,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13652,7 +13655,7 @@
       <c r="F64" s="14" t="n">
         <v>0.008709626849809912</v>
       </c>
-      <c r="G64" s="15" t="n">
+      <c r="G64" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -13660,7 +13663,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I64" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13687,7 +13690,7 @@
       <c r="F65" s="14" t="n">
         <v>0.009768500469533443</v>
       </c>
-      <c r="G65" s="15" t="n">
+      <c r="G65" s="13" t="n">
         <v>644.7691368702509</v>
       </c>
       <c r="H65" s="10" t="inlineStr">
@@ -13695,7 +13698,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I65" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -13722,7 +13725,7 @@
       <c r="F66" s="14" t="n">
         <v>0.003204458134143565</v>
       </c>
-      <c r="G66" s="15" t="n">
+      <c r="G66" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="10" t="inlineStr">
@@ -13730,7 +13733,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="I66" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13757,7 +13760,7 @@
       <c r="F67" s="14" t="n">
         <v>0.02413351051571942</v>
       </c>
-      <c r="G67" s="15" t="n">
+      <c r="G67" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="10" t="inlineStr">
@@ -13765,7 +13768,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13792,7 +13795,7 @@
       <c r="F68" s="14" t="n">
         <v>0.004247887855760608</v>
       </c>
-      <c r="G68" s="15" t="n">
+      <c r="G68" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H68" s="10" t="inlineStr">
@@ -13800,7 +13803,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I68" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13827,7 +13830,7 @@
       <c r="F69" s="14" t="n">
         <v>0.006988814254995765</v>
       </c>
-      <c r="G69" s="15" t="n">
+      <c r="G69" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="10" t="inlineStr">
@@ -13835,7 +13838,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13862,7 +13865,7 @@
       <c r="F70" s="14" t="n">
         <v>0.04370250371677853</v>
       </c>
-      <c r="G70" s="15" t="n">
+      <c r="G70" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H70" s="9" t="inlineStr">
@@ -13870,7 +13873,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13897,7 +13900,7 @@
       <c r="F71" s="14" t="n">
         <v>0.01293033268809812</v>
       </c>
-      <c r="G71" s="15" t="n">
+      <c r="G71" s="13" t="n">
         <v>903.8720142795978</v>
       </c>
       <c r="H71" s="10" t="inlineStr">
@@ -13905,7 +13908,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I71" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -13932,7 +13935,7 @@
       <c r="F72" s="14" t="n">
         <v>0.003738960541997562</v>
       </c>
-      <c r="G72" s="15" t="n">
+      <c r="G72" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="10" t="inlineStr">
@@ -13940,7 +13943,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13967,7 +13970,7 @@
       <c r="F73" s="14" t="n">
         <v>0.1753661812011368</v>
       </c>
-      <c r="G73" s="15" t="n">
+      <c r="G73" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -13975,7 +13978,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I73" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14002,7 +14005,7 @@
       <c r="F74" s="14" t="n">
         <v>0.1122930342223213</v>
       </c>
-      <c r="G74" s="15" t="n">
+      <c r="G74" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -14010,7 +14013,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I74" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14037,7 +14040,7 @@
       <c r="F75" s="14" t="n">
         <v>0.001570663006772549</v>
       </c>
-      <c r="G75" s="15" t="n">
+      <c r="G75" s="13" t="n">
         <v>6724.774965127542</v>
       </c>
       <c r="H75" s="10" t="inlineStr">
@@ -14045,7 +14048,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -14072,7 +14075,7 @@
       <c r="F76" s="14" t="n">
         <v>0.05042764838335538</v>
       </c>
-      <c r="G76" s="15" t="n">
+      <c r="G76" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -14080,7 +14083,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I76" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14107,7 +14110,7 @@
       <c r="F77" s="14" t="n">
         <v>0.01009422793922765</v>
       </c>
-      <c r="G77" s="15" t="n">
+      <c r="G77" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="10" t="inlineStr">
@@ -14115,7 +14118,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I77" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14142,7 +14145,7 @@
       <c r="F78" s="14" t="n">
         <v>0.09343330921184313</v>
       </c>
-      <c r="G78" s="15" t="n">
+      <c r="G78" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -14150,7 +14153,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I78" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14177,7 +14180,7 @@
       <c r="F79" s="14" t="n">
         <v>0.005847516903707157</v>
       </c>
-      <c r="G79" s="15" t="n">
+      <c r="G79" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="10" t="inlineStr">
@@ -14185,7 +14188,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14212,7 +14215,7 @@
       <c r="F80" s="14" t="n">
         <v>0.0006533042377219214</v>
       </c>
-      <c r="G80" s="15" t="n">
+      <c r="G80" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H80" s="10" t="inlineStr">
@@ -14220,7 +14223,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I80" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14247,7 +14250,7 @@
       <c r="F81" s="14" t="n">
         <v>0.0005901674726668149</v>
       </c>
-      <c r="G81" s="15" t="n">
+      <c r="G81" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="10" t="inlineStr">
@@ -14255,7 +14258,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14282,7 +14285,7 @@
       <c r="F82" s="14" t="n">
         <v>0.001682002572474523</v>
       </c>
-      <c r="G82" s="15" t="n">
+      <c r="G82" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="10" t="inlineStr">
@@ -14290,7 +14293,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14317,7 +14320,7 @@
       <c r="F83" s="14" t="n">
         <v>0.0004811202937222332</v>
       </c>
-      <c r="G83" s="15" t="n">
+      <c r="G83" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="10" t="inlineStr">
@@ -14325,7 +14328,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I83" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14352,7 +14355,7 @@
       <c r="F84" s="14" t="n">
         <v>0.001237129165320073</v>
       </c>
-      <c r="G84" s="15" t="n">
+      <c r="G84" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="10" t="inlineStr">
@@ -14360,7 +14363,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="I84" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14387,7 +14390,7 @@
       <c r="F85" s="14" t="n">
         <v>0.0004346172651708589</v>
       </c>
-      <c r="G85" s="15" t="n">
+      <c r="G85" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -14395,7 +14398,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="I85" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14422,7 +14425,7 @@
       <c r="F86" s="14" t="n">
         <v>0.0002756479540393306</v>
       </c>
-      <c r="G86" s="15" t="n">
+      <c r="G86" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H86" s="10" t="inlineStr">
@@ -14430,7 +14433,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr">
+      <c r="I86" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14457,7 +14460,7 @@
       <c r="F87" s="14" t="n">
         <v>0.0008769247208026441</v>
       </c>
-      <c r="G87" s="15" t="n">
+      <c r="G87" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H87" s="10" t="inlineStr">
@@ -14465,7 +14468,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I87" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14492,7 +14495,7 @@
       <c r="F88" s="14" t="n">
         <v>0.01919754629612355</v>
       </c>
-      <c r="G88" s="15" t="n">
+      <c r="G88" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="10" t="inlineStr">
@@ -14500,7 +14503,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="I88" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14527,7 +14530,7 @@
       <c r="F89" s="14" t="n">
         <v>0.01791144884566429</v>
       </c>
-      <c r="G89" s="15" t="n">
+      <c r="G89" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="10" t="inlineStr">
@@ -14535,7 +14538,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I89" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14562,7 +14565,7 @@
       <c r="F90" s="14" t="n">
         <v>0.07261855107802875</v>
       </c>
-      <c r="G90" s="15" t="n">
+      <c r="G90" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -14570,7 +14573,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr">
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14597,7 +14600,7 @@
       <c r="F91" s="14" t="n">
         <v>0.007805865693931421</v>
       </c>
-      <c r="G91" s="15" t="n">
+      <c r="G91" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -14605,7 +14608,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="I91" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14632,7 +14635,7 @@
       <c r="F92" s="14" t="n">
         <v>0.006696536108300814</v>
       </c>
-      <c r="G92" s="15" t="n">
+      <c r="G92" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -14640,7 +14643,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="I92" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14667,7 +14670,7 @@
       <c r="F93" s="14" t="n">
         <v>0.01212097318229208</v>
       </c>
-      <c r="G93" s="15" t="n">
+      <c r="G93" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="10" t="inlineStr">
@@ -14675,7 +14678,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I93" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14702,7 +14705,7 @@
       <c r="F94" s="14" t="n">
         <v>0.1612320219161404</v>
       </c>
-      <c r="G94" s="15" t="n">
+      <c r="G94" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="8" t="inlineStr">
@@ -14710,7 +14713,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14737,7 +14740,7 @@
       <c r="F95" s="14" t="n">
         <v>0.06427101472217825</v>
       </c>
-      <c r="G95" s="15" t="n">
+      <c r="G95" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -14745,7 +14748,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
+      <c r="I95" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14772,7 +14775,7 @@
       <c r="F96" s="14" t="n">
         <v>0.006079253952870533</v>
       </c>
-      <c r="G96" s="15" t="n">
+      <c r="G96" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H96" s="10" t="inlineStr">
@@ -14780,7 +14783,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I96" s="5" t="inlineStr">
+      <c r="I96" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14807,7 +14810,7 @@
       <c r="F97" s="14" t="n">
         <v>0.002520762223993569</v>
       </c>
-      <c r="G97" s="15" t="n">
+      <c r="G97" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H97" s="10" t="inlineStr">
@@ -14815,7 +14818,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="I97" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14842,7 +14845,7 @@
       <c r="F98" s="14" t="n">
         <v>0.00640156544831924</v>
       </c>
-      <c r="G98" s="15" t="n">
+      <c r="G98" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H98" s="10" t="inlineStr">
@@ -14850,7 +14853,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I98" s="5" t="inlineStr">
+      <c r="I98" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14877,7 +14880,7 @@
       <c r="F99" s="14" t="n">
         <v>0.1643548533003649</v>
       </c>
-      <c r="G99" s="15" t="n">
+      <c r="G99" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H99" s="8" t="inlineStr">
@@ -14885,7 +14888,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I99" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14912,7 +14915,7 @@
       <c r="F100" s="14" t="n">
         <v>0.02696274630541872</v>
       </c>
-      <c r="G100" s="15" t="n">
+      <c r="G100" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="10" t="inlineStr">
@@ -14920,7 +14923,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="I100" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14947,7 +14950,7 @@
       <c r="F101" s="14" t="n">
         <v>0.002717435521926613</v>
       </c>
-      <c r="G101" s="15" t="n">
+      <c r="G101" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="10" t="inlineStr">
@@ -14955,7 +14958,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I101" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14982,7 +14985,7 @@
       <c r="F102" s="14" t="n">
         <v>0.05451695404669582</v>
       </c>
-      <c r="G102" s="15" t="n">
+      <c r="G102" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H102" s="8" t="inlineStr">
@@ -14990,7 +14993,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="I102" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -15017,7 +15020,7 @@
       <c r="F103" s="14" t="n">
         <v>0.0008002684771665334</v>
       </c>
-      <c r="G103" s="15" t="n">
+      <c r="G103" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="10" t="inlineStr">
@@ -15025,7 +15028,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr">
+      <c r="I103" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -15052,7 +15055,7 @@
       <c r="F104" s="14" t="n">
         <v>0.09053285534638413</v>
       </c>
-      <c r="G104" s="15" t="n">
+      <c r="G104" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H104" s="8" t="inlineStr">
@@ -15060,7 +15063,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I104" s="5" t="inlineStr">
+      <c r="I104" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -15087,7 +15090,7 @@
       <c r="F105" s="14" t="n">
         <v>0.007935030711507755</v>
       </c>
-      <c r="G105" s="15" t="n">
+      <c r="G105" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H105" s="10" t="inlineStr">
@@ -15095,7 +15098,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="I105" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -15122,7 +15125,7 @@
       <c r="F106" s="14" t="n">
         <v>0.01100901096944579</v>
       </c>
-      <c r="G106" s="15" t="n">
+      <c r="G106" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="10" t="inlineStr">
@@ -15130,7 +15133,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="I106" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -15157,7 +15160,7 @@
       <c r="F107" s="14" t="n">
         <v>0.3047452888902493</v>
       </c>
-      <c r="G107" s="15" t="n">
+      <c r="G107" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="7" t="inlineStr">
@@ -15165,7 +15168,7 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I107" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>

--- a/rates-nodispo/week-19/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-19/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7867,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9710,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11553,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
